--- a/mappingCorps/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRMedicationAdministrationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="94">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMTraitement vers le profil CDA FRCDATraitement, puis vers le profil FHIR FRMedicationAdministrationDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMMedicationAdministration vers le profil CDA FRCDATraitement (Groupe 1), et vers le profil FHIR FRMedicationAdministrationDocument (Groupe 2).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-administration</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement</t>
   </si>
   <si>
-    <t>FRLMTraitement</t>
+    <t>FRLMMedicationAdministration</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,106 +118,124 @@
     <t>FRCDATraitement</t>
   </si>
   <si>
-    <t>FRLMTraitement.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.id</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.code</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.code</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.note</t>
+    <t>FRLMMedicationAdministration.medication</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.consumable</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime[not(@operator='A')]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime[@operator='A']</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.reason[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.entryRelationship:frTraitement.entryRelationship:frReferenceInterne</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.renderedDosageInstruction</t>
   </si>
   <si>
     <t>FRCDATraitement.text</t>
   </si>
   <si>
-    <t>FRLMTraitement.status</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.occurancePeriod</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[not(@operator='A')]</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.occuranceDateTim</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[@operator='A']</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.route</t>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.note</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.doseQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.rateQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.numberOfTimes</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime.frequency</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.period</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime.period</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.frequency.additionalInstructions</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.dateOfAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.conditionOfAdministration</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.precondition</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.date[x]</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.eventTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.routeOfAdministration</t>
   </si>
   <si>
     <t>FRCDATraitement.routeCode</t>
   </si>
   <si>
-    <t>FRLMTraitement.dosage.site</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.approachSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.dose</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.doseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.rate[x]</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.rateQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.doseMaximale</t>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerPeriod.quantity</t>
   </si>
   <si>
     <t>FRCDATraitement.maxDoseQuantity</t>
   </si>
   <si>
-    <t>FRLMTraitement.medicament</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.consumable</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.reason</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frReferenceInterne</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.prescription</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frPrescription</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.subordinateTreatment</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frTraitementSubordonne</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.instructionsPatient</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.precondition</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.precondition</t>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerPeriod.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosageInstructions.dosageDetails.maxLifetimeDose</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.note</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-administration-document</t>
@@ -226,16 +244,7 @@
     <t>FRMedicationAdministrationDocument</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.category</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.category.text</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.status</t>
+    <t>FRMedicationAdministrationDocument.medication:FRMedicationDocument</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.effectivePeriod</t>
@@ -244,34 +253,46 @@
     <t>FRMedicationAdministrationDocument.extension:medicationAdministration-occurence-r5</t>
   </si>
   <si>
+    <t>FRMedicationAdministrationDocument.reasonReference</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument.reasonCode</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument.dosage</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationAdministrationDocument.dosage.text</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.routeOfAdministration</t>
+  </si>
+  <si>
     <t>FRMedicationAdministrationDocument.dosage.route</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.dosage.site</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.dose[x]</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.dosage.dose</t>
   </si>
   <si>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
     <t>FRMedicationAdministrationDocument.dosage.rate[x]</t>
   </si>
   <si>
-    <t>FRMedicationAdministrationDocument.dosage.rateRatio</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.medication:FRMedicationDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.reasonReference</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.request</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.medication:FRMedicationsCombinaisonDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationAdministrationDocument.dosage.text</t>
+    <t>FRLMMedicationAdministration.dosage.dosageDetails.sequence</t>
+  </si>
+  <si>
+    <t>FRLMMedicationAdministration.dosage.extension:FRMedicationAdministrationSequenceExtension</t>
   </si>
   <si>
     <t>FRMedicationAdministrationDocument.note</t>
@@ -526,7 +547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -604,198 +625,315 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E29" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -804,7 +942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -826,7 +964,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -835,7 +973,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -843,237 +981,172 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="E20" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
